--- a/artfynd/A 36141-2023 artfynd.xlsx
+++ b/artfynd/A 36141-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36141-2023 artfynd.xlsx
+++ b/artfynd/A 36141-2023 artfynd.xlsx
@@ -12839,7 +12839,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119637996</v>
+        <v>119637950</v>
       </c>
       <c r="B113" t="n">
         <v>90067</v>
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>697888</v>
+        <v>697899</v>
       </c>
       <c r="R113" t="n">
-        <v>7316794</v>
+        <v>7316795</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12945,7 +12945,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119637950</v>
+        <v>119637996</v>
       </c>
       <c r="B114" t="n">
         <v>90067</v>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>697899</v>
+        <v>697888</v>
       </c>
       <c r="R114" t="n">
-        <v>7316795</v>
+        <v>7316794</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>

--- a/artfynd/A 36141-2023 artfynd.xlsx
+++ b/artfynd/A 36141-2023 artfynd.xlsx
@@ -12627,10 +12627,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119638030</v>
+        <v>119637950</v>
       </c>
       <c r="B111" t="n">
-        <v>89252</v>
+        <v>90067</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12639,25 +12639,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6276</v>
+        <v>256703</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12670,10 +12670,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>697792</v>
+        <v>697899</v>
       </c>
       <c r="R111" t="n">
-        <v>7316708</v>
+        <v>7316795</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12839,7 +12839,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119637950</v>
+        <v>119637996</v>
       </c>
       <c r="B113" t="n">
         <v>90067</v>
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>697899</v>
+        <v>697888</v>
       </c>
       <c r="R113" t="n">
-        <v>7316795</v>
+        <v>7316794</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12945,10 +12945,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119637996</v>
+        <v>119638030</v>
       </c>
       <c r="B114" t="n">
-        <v>90067</v>
+        <v>89252</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12957,25 +12957,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>256703</v>
+        <v>6276</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>697888</v>
+        <v>697792</v>
       </c>
       <c r="R114" t="n">
-        <v>7316794</v>
+        <v>7316708</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>

--- a/artfynd/A 36141-2023 artfynd.xlsx
+++ b/artfynd/A 36141-2023 artfynd.xlsx
@@ -12733,10 +12733,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119638090</v>
+        <v>119638030</v>
       </c>
       <c r="B112" t="n">
-        <v>91463</v>
+        <v>89252</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12745,25 +12745,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4745</v>
+        <v>6276</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12776,10 +12776,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>697671</v>
+        <v>697792</v>
       </c>
       <c r="R112" t="n">
-        <v>7316656</v>
+        <v>7316708</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12945,10 +12945,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119638030</v>
+        <v>119638090</v>
       </c>
       <c r="B114" t="n">
-        <v>89252</v>
+        <v>91463</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12957,25 +12957,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6276</v>
+        <v>4745</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>697792</v>
+        <v>697671</v>
       </c>
       <c r="R114" t="n">
-        <v>7316708</v>
+        <v>7316656</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>

--- a/artfynd/A 36141-2023 artfynd.xlsx
+++ b/artfynd/A 36141-2023 artfynd.xlsx
@@ -13054,7 +13054,7 @@
         <v>119796331</v>
       </c>
       <c r="B115" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
